--- a/docs/project-management/budget.xlsx
+++ b/docs/project-management/budget.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C763090-99EE-6346-9C2B-E7733253CC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AA724A-F0FA-274A-ACE6-F66A6688EAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17220" yWindow="9400" windowWidth="17700" windowHeight="13440" xr2:uid="{2E5C18CF-13B3-B440-AB6A-7CD7A53951E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -534,7 +534,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="2">
-        <v>192</v>
+        <v>121.98</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -567,7 +567,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="2">
-        <v>169</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -595,7 +595,7 @@
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C10" s="2">
         <f>SUM(C2:C9)</f>
-        <v>600</v>
+        <v>499.98</v>
       </c>
     </row>
   </sheetData>
